--- a/data/sample_summary/2026/1-6月/1-6月客户类型样本统计表.xlsx
+++ b/data/sample_summary/2026/1-6月/1-6月客户类型样本统计表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhangqijin/PycharmProjects/hangbo/data/sample_summary/2026/1-6月/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C74A692-F133-6E40-8F09-E70E25ED7669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A4E862-D88D-D945-B4F6-421CDA1D97F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20480" yWindow="600" windowWidth="20480" windowHeight="21200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="40960" windowHeight="21200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="样本统计" sheetId="1" r:id="rId1"/>
@@ -662,11 +662,11 @@
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D28" si="0">IFERROR(E3/C3,0)</f>
-        <v>0.76315789473684215</v>
+        <v>0.78947368421052633</v>
       </c>
       <c r="E3" s="3">
         <f t="shared" ref="E3:E9" si="1">SUM(F3:J3)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" s="3">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>5</v>
       </c>
       <c r="J3" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="24" customHeight="1">
@@ -694,11 +694,11 @@
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>0.44598337950138506</v>
+        <v>0.46398891966759004</v>
       </c>
       <c r="E4" s="3">
         <f t="shared" si="1"/>
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="F4" s="3">
         <v>24</v>
@@ -713,7 +713,7 @@
         <v>62</v>
       </c>
       <c r="J4" s="3">
-        <v>75</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="24" customHeight="1">
@@ -726,11 +726,11 @@
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>0.43870967741935485</v>
+        <v>0.47634408602150535</v>
       </c>
       <c r="E5" s="3">
         <f t="shared" si="1"/>
-        <v>408</v>
+        <v>443</v>
       </c>
       <c r="F5" s="3">
         <v>30</v>
@@ -745,7 +745,7 @@
         <v>77</v>
       </c>
       <c r="J5" s="3">
-        <v>88</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="24" customHeight="1">
@@ -790,11 +790,11 @@
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>0.68421052631578949</v>
+        <v>0.71052631578947367</v>
       </c>
       <c r="E7" s="3">
         <f t="shared" si="1"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7" s="3">
         <v>7</v>
@@ -809,7 +809,7 @@
         <v>6</v>
       </c>
       <c r="J7" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="24" customHeight="1">
@@ -822,11 +822,11 @@
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>0.55483870967741933</v>
+        <v>0.57096774193548383</v>
       </c>
       <c r="E8" s="3">
         <f t="shared" si="1"/>
-        <v>516</v>
+        <v>531</v>
       </c>
       <c r="F8" s="3">
         <v>183</v>
@@ -841,7 +841,7 @@
         <v>107</v>
       </c>
       <c r="J8" s="3">
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="24" customHeight="1">
@@ -887,11 +887,11 @@
       </c>
       <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>0.48207754206291148</v>
+        <v>0.50585223116313094</v>
       </c>
       <c r="E10" s="3">
         <f t="shared" ref="E10:J10" si="2">SUM(E3:E9)</f>
-        <v>1318</v>
+        <v>1383</v>
       </c>
       <c r="F10" s="3">
         <f t="shared" si="2"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="J10" s="3">
         <f t="shared" si="2"/>
-        <v>191</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="24" customHeight="1">
@@ -926,14 +926,14 @@
       </c>
       <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>0.52280701754385961</v>
+        <v>0.57894736842105265</v>
       </c>
       <c r="E11" s="3">
         <f>SUM(F11:J11)</f>
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="F11" s="3">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G11" s="3">
         <v>29</v>
@@ -945,7 +945,7 @@
         <v>16</v>
       </c>
       <c r="J11" s="3">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="24" customHeight="1">
@@ -958,11 +958,11 @@
       </c>
       <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>0.3719298245614035</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="E12" s="3">
         <f>SUM(F12:J12)</f>
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="F12" s="3">
         <v>0</v>
@@ -977,7 +977,7 @@
         <v>28</v>
       </c>
       <c r="J12" s="3">
-        <v>30</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="24" customHeight="1">
@@ -1022,11 +1022,11 @@
       </c>
       <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>0.13157894736842105</v>
+        <v>0.13815789473684212</v>
       </c>
       <c r="E14" s="3">
         <f>SUM(F14:J14)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F14" s="3">
         <v>1</v>
@@ -1041,7 +1041,7 @@
         <v>2</v>
       </c>
       <c r="J14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="24" customHeight="1">
@@ -1087,15 +1087,15 @@
       </c>
       <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>0.43609022556390975</v>
+        <v>0.48335123523093448</v>
       </c>
       <c r="E16" s="3">
         <f t="shared" ref="E16:J16" si="3">SUM(E11:E15)</f>
-        <v>406</v>
+        <v>450</v>
       </c>
       <c r="F16" s="3">
         <f t="shared" si="3"/>
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G16" s="3">
         <f t="shared" si="3"/>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="J16" s="3">
         <f t="shared" si="3"/>
-        <v>62</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="24" customHeight="1">
@@ -1126,11 +1126,11 @@
       </c>
       <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>0.45333333333333331</v>
+        <v>0.57333333333333336</v>
       </c>
       <c r="E17" s="3">
         <f>SUM(F17:J17)</f>
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F17" s="3">
         <v>0</v>
@@ -1145,7 +1145,7 @@
         <v>5</v>
       </c>
       <c r="J17" s="3">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="24" customHeight="1">
@@ -1158,11 +1158,11 @@
       </c>
       <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>0.26666666666666666</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E18" s="3">
         <f>SUM(F18:J18)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18" s="3">
         <v>0</v>
@@ -1177,7 +1177,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="24" customHeight="1">
@@ -1191,11 +1191,11 @@
       </c>
       <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>0.42222222222222222</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="E19" s="3">
         <f t="shared" ref="E19:J19" si="4">SUM(E17:E18)</f>
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F19" s="3">
         <f t="shared" si="4"/>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="J19" s="3">
         <f t="shared" si="4"/>
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="24" customHeight="1">
@@ -1262,11 +1262,11 @@
       </c>
       <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="E21" s="3">
         <f t="shared" si="5"/>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F21" s="3">
         <v>0</v>
@@ -1281,7 +1281,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="24" customHeight="1">
@@ -1294,11 +1294,11 @@
       </c>
       <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>0.56666666666666665</v>
+        <v>0.62666666666666671</v>
       </c>
       <c r="E22" s="3">
         <f t="shared" si="5"/>
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="F22" s="3">
         <v>47</v>
@@ -1313,7 +1313,7 @@
         <v>18</v>
       </c>
       <c r="J22" s="3">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="24" customHeight="1">
@@ -1390,14 +1390,14 @@
       </c>
       <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>0.25187969924812031</v>
+        <v>0.24436090225563908</v>
       </c>
       <c r="E25" s="3">
         <f t="shared" si="5"/>
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F25" s="3">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G25" s="3">
         <v>6</v>
@@ -1409,7 +1409,7 @@
         <v>14</v>
       </c>
       <c r="J25" s="3">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="24" customHeight="1">
@@ -1423,15 +1423,15 @@
       </c>
       <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>0.41666666666666669</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="E26" s="3">
         <f t="shared" ref="E26:J26" si="6">SUM(E21:E25)</f>
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F26" s="3">
         <f t="shared" si="6"/>
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G26" s="3">
         <f t="shared" si="6"/>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J26" s="3">
         <f t="shared" si="6"/>
-        <v>80</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="24" customHeight="1">
@@ -1460,11 +1460,11 @@
       </c>
       <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E27" s="3">
         <f>SUM(F27:J27)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="3">
         <v>0</v>
@@ -1479,7 +1479,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="28" customHeight="1">
@@ -1493,11 +1493,11 @@
       </c>
       <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>0.44437086092715233</v>
+        <v>0.47306843267108167</v>
       </c>
       <c r="E28" s="3">
         <f t="shared" ref="E28:J28" si="7">SUM(E3:E9,E11:E15,E17:E18,E20:E20,E21:E25,E27:E27)</f>
-        <v>2013</v>
+        <v>2143</v>
       </c>
       <c r="F28" s="3">
         <f t="shared" si="7"/>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="J28" s="3">
         <f t="shared" si="7"/>
-        <v>356</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>
